--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87376</v>
+        <v>87382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87551</v>
+        <v>87557</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87551</v>
+        <v>87557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89272</v>
+        <v>89278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105307</v>
       </c>
       <c r="B33" t="n">
-        <v>90855</v>
+        <v>90861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105278</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87558</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105291</v>
       </c>
       <c r="B35" t="n">
-        <v>87552</v>
+        <v>87558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105294</v>
       </c>
       <c r="B36" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105344</v>
       </c>
       <c r="B37" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137105346</v>
       </c>
       <c r="B38" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106623</v>
       </c>
       <c r="B39" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137106626</v>
       </c>
       <c r="B40" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>137105280</v>
       </c>
       <c r="B41" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>137105282</v>
       </c>
       <c r="B42" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>137105285</v>
       </c>
       <c r="B43" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>137105286</v>
       </c>
       <c r="B44" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137105296</v>
       </c>
       <c r="B45" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>137105303</v>
       </c>
       <c r="B46" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>137105306</v>
       </c>
       <c r="B47" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137105308</v>
       </c>
       <c r="B48" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137106634</v>
       </c>
       <c r="B49" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>137105304</v>
       </c>
       <c r="B50" t="n">
-        <v>90799</v>
+        <v>90805</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87557</v>
+        <v>87561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87557</v>
+        <v>87561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91530</v>
+        <v>91534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89278</v>
+        <v>89282</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,32 +4145,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137105307</v>
+        <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>90861</v>
+        <v>87562</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>245042</v>
+        <v>248947</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4180,13 +4180,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>724354</v>
+        <v>724155</v>
       </c>
       <c r="R33" t="n">
-        <v>6390432</v>
+        <v>6390503</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4251,16 +4251,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105307</t>
+          <t>https://artportalen.se/Sighting/137105278</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137105278</v>
+        <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>724155</v>
+        <v>724291</v>
       </c>
       <c r="R34" t="n">
-        <v>6390503</v>
+        <v>6390455</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,16 +4363,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105278</t>
+          <t>https://artportalen.se/Sighting/137105291</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137105291</v>
+        <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87558</v>
+        <v>87455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4380,21 +4380,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>248947</v>
+        <v>248956</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>724291</v>
+        <v>724302</v>
       </c>
       <c r="R35" t="n">
-        <v>6390455</v>
+        <v>6390487</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4475,16 +4475,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105291</t>
+          <t>https://artportalen.se/Sighting/137105294</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137105294</v>
+        <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>724302</v>
+        <v>724345</v>
       </c>
       <c r="R36" t="n">
-        <v>6390487</v>
+        <v>6390410</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,16 +4587,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105294</t>
+          <t>https://artportalen.se/Sighting/137105344</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137105344</v>
+        <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>724345</v>
+        <v>724300</v>
       </c>
       <c r="R37" t="n">
         <v>6390410</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,16 +4699,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105344</t>
+          <t>https://artportalen.se/Sighting/137105346</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137105346</v>
+        <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>724300</v>
+        <v>724302</v>
       </c>
       <c r="R38" t="n">
-        <v>6390410</v>
+        <v>6390475</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,27 +4800,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105346</t>
+          <t>https://artportalen.se/Sighting/137106623</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137106623</v>
+        <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>724302</v>
+        <v>724306</v>
       </c>
       <c r="R39" t="n">
-        <v>6390475</v>
+        <v>6390470</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,38 +4923,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106623</t>
+          <t>https://artportalen.se/Sighting/137106626</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137106626</v>
+        <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87451</v>
+        <v>87539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4964,13 +4964,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>724306</v>
+        <v>724207</v>
       </c>
       <c r="R40" t="n">
-        <v>6390470</v>
+        <v>6390497</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,33 +5018,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137106626</t>
+          <t>https://artportalen.se/Sighting/137105280</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137105280</v>
+        <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5076,10 +5077,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>724207</v>
+        <v>724230</v>
       </c>
       <c r="R41" t="n">
-        <v>6390497</v>
+        <v>6390495</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5148,16 +5149,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105280</t>
+          <t>https://artportalen.se/Sighting/137105282</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137105282</v>
+        <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5189,10 +5190,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>724230</v>
+        <v>724215</v>
       </c>
       <c r="R42" t="n">
-        <v>6390495</v>
+        <v>6390435</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5224,7 +5225,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5234,7 +5235,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5261,16 +5262,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105282</t>
+          <t>https://artportalen.se/Sighting/137105285</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137105285</v>
+        <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5302,13 +5303,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>724215</v>
+        <v>724217</v>
       </c>
       <c r="R43" t="n">
-        <v>6390435</v>
+        <v>6390461</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5337,7 +5338,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5347,7 +5348,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5374,16 +5375,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105285</t>
+          <t>https://artportalen.se/Sighting/137105286</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137105286</v>
+        <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5415,10 +5416,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>724217</v>
+        <v>724297</v>
       </c>
       <c r="R44" t="n">
-        <v>6390461</v>
+        <v>6390481</v>
       </c>
       <c r="S44" t="n">
         <v>11</v>
@@ -5450,7 +5451,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5460,7 +5461,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5487,16 +5488,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105286</t>
+          <t>https://artportalen.se/Sighting/137105296</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137105296</v>
+        <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,13 +5529,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>724297</v>
+        <v>724340</v>
       </c>
       <c r="R45" t="n">
-        <v>6390481</v>
+        <v>6390487</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5563,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5573,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5600,16 +5601,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105296</t>
+          <t>https://artportalen.se/Sighting/137105303</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137105303</v>
+        <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5641,10 +5642,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>724340</v>
+        <v>724338</v>
       </c>
       <c r="R46" t="n">
-        <v>6390487</v>
+        <v>6390421</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5676,7 +5677,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5686,7 +5687,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,16 +5714,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105303</t>
+          <t>https://artportalen.se/Sighting/137105306</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137105306</v>
+        <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5754,13 +5755,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>724338</v>
+        <v>724374</v>
       </c>
       <c r="R47" t="n">
-        <v>6390421</v>
+        <v>6390424</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5789,7 +5790,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5799,7 +5800,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5826,16 +5827,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105306</t>
+          <t>https://artportalen.se/Sighting/137105308</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137105308</v>
+        <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5861,19 +5862,22 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gothem Båtare, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>724374</v>
+        <v>724371</v>
       </c>
       <c r="R48" t="n">
-        <v>6390424</v>
+        <v>6390419</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5902,7 +5906,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5912,7 +5916,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5928,68 +5932,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137105308</t>
+          <t>https://artportalen.se/Sighting/137106634</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137106634</v>
+        <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>87535</v>
+        <v>90809</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>6049769</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clitopaxillus alexandri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Gillet) G.Moreno &amp; al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gothem Båtare, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>724371</v>
+        <v>724353</v>
       </c>
       <c r="R49" t="n">
-        <v>6390419</v>
+        <v>6390471</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6018,7 +6014,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6028,7 +6024,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6044,124 +6040,16 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137106634</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>137105304</v>
-      </c>
-      <c r="B50" t="n">
-        <v>90805</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>6049769</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Clitopaxillus alexandri</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Gillet) G.Moreno &amp; al.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Gothem Båtare, Gtl</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>724353</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6390471</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Gothem</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137105304</t>
         </is>
@@ -6217,7 +6105,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91534</v>
+        <v>91536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89282</v>
+        <v>89284</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90809</v>
+        <v>90811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91536</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89284</v>
+        <v>89297</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90811</v>
+        <v>90824</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89297</v>
+        <v>89299</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90824</v>
+        <v>90826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89299</v>
+        <v>89302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90826</v>
+        <v>90829</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91554</v>
+        <v>91564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89302</v>
+        <v>89312</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90829</v>
+        <v>90839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89312</v>
+        <v>89313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90839</v>
+        <v>90840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91565</v>
+        <v>91568</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89313</v>
+        <v>89316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90840</v>
+        <v>90843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91568</v>
+        <v>91570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
+        <v>91575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89316</v>
+        <v>89321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90843</v>
+        <v>90848</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91575</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89321</v>
+        <v>89332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90848</v>
+        <v>90859</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89332</v>
+        <v>89333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90859</v>
+        <v>90860</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91588</v>
+        <v>91591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89333</v>
+        <v>89336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90860</v>
+        <v>90863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 9540-2026 artfynd.xlsx
+++ b/artfynd/A 9540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105287</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105295</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137106620</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137105301</v>
       </c>
       <c r="B5" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137105343</v>
       </c>
       <c r="B6" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137106624</v>
       </c>
       <c r="B7" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137105290</v>
       </c>
       <c r="B8" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>137106628</v>
       </c>
       <c r="B9" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137106617</v>
       </c>
       <c r="B10" t="n">
-        <v>91591</v>
+        <v>91595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>137105347</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137105351</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>137105279</v>
       </c>
       <c r="B13" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>137105281</v>
       </c>
       <c r="B14" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137105299</v>
       </c>
       <c r="B15" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137105302</v>
       </c>
       <c r="B16" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>137105309</v>
       </c>
       <c r="B17" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>137105348</v>
       </c>
       <c r="B18" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>137105349</v>
       </c>
       <c r="B19" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>137106616</v>
       </c>
       <c r="B20" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>137106619</v>
       </c>
       <c r="B21" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>137106632</v>
       </c>
       <c r="B22" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>137106633</v>
       </c>
       <c r="B23" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>137106635</v>
       </c>
       <c r="B24" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137105283</v>
       </c>
       <c r="B25" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>137105292</v>
       </c>
       <c r="B26" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>137105345</v>
       </c>
       <c r="B27" t="n">
-        <v>89336</v>
+        <v>89340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>137105356</v>
       </c>
       <c r="B28" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>137106625</v>
       </c>
       <c r="B29" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>137105293</v>
       </c>
       <c r="B30" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>137105300</v>
       </c>
       <c r="B31" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>137105284</v>
       </c>
       <c r="B32" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>137105278</v>
       </c>
       <c r="B33" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>137105291</v>
       </c>
       <c r="B34" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137105294</v>
       </c>
       <c r="B35" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137105344</v>
       </c>
       <c r="B36" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>137105346</v>
       </c>
       <c r="B37" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137106623</v>
       </c>
       <c r="B38" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137106626</v>
       </c>
       <c r="B39" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137105280</v>
       </c>
       <c r="B40" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>137105282</v>
       </c>
       <c r="B41" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>137105285</v>
       </c>
       <c r="B42" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>137105286</v>
       </c>
       <c r="B43" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>137105296</v>
       </c>
       <c r="B44" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>137105303</v>
       </c>
       <c r="B45" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>137105306</v>
       </c>
       <c r="B46" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137105308</v>
       </c>
       <c r="B47" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>137106634</v>
       </c>
       <c r="B48" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>137105304</v>
       </c>
       <c r="B49" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
